--- a/logs/fio/20251116_1354/perf_timeline.xlsx
+++ b/logs/fio/20251116_1354/perf_timeline.xlsx
@@ -1,40 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NosLab-Windows\Github\ldy\logs\fio\20251116_1354\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393D9D6B-E75E-4B91-A12D-9FF170A82BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="128KB-seq-read.fio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="128KB-seq-write.fio" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="4KB-rand-read.fio" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4KB-rand-write.fio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="128KB-seq-read.fio" sheetId="1" r:id="rId1"/>
+    <sheet name="128KB-seq-write.fio" sheetId="2" r:id="rId2"/>
+    <sheet name="4KB-rand-read.fio" sheetId="3" r:id="rId3"/>
+    <sheet name="4KB-rand-write.fio" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="13">
+  <si>
+    <t>time(sec)</t>
+  </si>
+  <si>
+    <t>10w.L1-dcache-load-misses</t>
+  </si>
+  <si>
+    <t>10w.cpu-migrations</t>
+  </si>
+  <si>
+    <t>10w.dTLB-load-misses</t>
+  </si>
+  <si>
+    <t>cpu.L1-dcache-load-misses</t>
+  </si>
+  <si>
+    <t>cpu.cpu-migrations</t>
+  </si>
+  <si>
+    <t>cpu.dTLB-load-misses</t>
+  </si>
+  <si>
+    <t>rr.L1-dcache-load-misses</t>
+  </si>
+  <si>
+    <t>rr.cpu-migrations</t>
+  </si>
+  <si>
+    <t>rr.dTLB-load-misses</t>
+  </si>
+  <si>
+    <t>thr.L1-dcache-load-misses</t>
+  </si>
+  <si>
+    <t>thr.cpu-migrations</t>
+  </si>
+  <si>
+    <t>thr.dTLB-load-misses</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,93 +108,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -423,5532 +432,5416 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>time(sec)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>10w.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>10w.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>10w.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>rr.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>rr.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>rr.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>thr.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>thr.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>thr.dTLB-load-misses</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>214186285</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>3674</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>1602151</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>206897144</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>3242</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>1375058</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>207039133</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>3627</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>1425049</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>220013951</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>3631</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>1614622</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>385674894</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>7096</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>2584006</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>383061012</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>6879</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>2172622</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>389805512</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>7224</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>2326081</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>385406414</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>6905</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>2229188</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>385309308</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>6777</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>2433685</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>393086632</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>6865</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>2145890</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>397629985</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>7101</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>2288451</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>392780421</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>6870</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>2295837</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>397047179</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7048</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>2424386</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>394339957</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>6882</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>1999169</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>403942840</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>7036</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>2123320</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>399489693</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>6852</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>2206936</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>398785107</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>7426</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>2417441</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>404814798</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>7201</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>2045382</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>402610075</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>7700</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>2162289</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>401679861</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>7277</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>2131602</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>393784523</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>6946</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>2419937</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>397397147</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>7555</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>2101809</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>398264393</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>7252</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>2248447</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>396882111</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>7329</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>2231445</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>408812519</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8796</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>2673489</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>408667753</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>8531</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>2151065</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>410614255</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>7774</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>2083160</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>402103009</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>8625</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>2194361</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>310198773</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>5390</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>1804232</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>326761113</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>5540</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1834940</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>317087092</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>5853</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>1805579</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>327204410</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>5631</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>1875107</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>447672162</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>7597</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>3133430</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>446876106</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>8156</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>2802629</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>444580928</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>7608</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>3008103</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>450520134</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>8162</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>3024746</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>446376081</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>7526</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>2364071</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>447498604</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>7535</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2258820</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>449151178</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>7876</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>2257314</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>455760575</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>7478</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>2542702</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>440291108</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>7608</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>2235118</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>446246922</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>7577</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>2150012</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>444830670</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>7614</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>2091347</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>447760015</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>7797</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>2239352</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>458499728</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>7751</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>2187844</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>464155897</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>7019</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>2170684</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>455130489</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>7748</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>2201388</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>459589415</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>7872</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>2216288</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>453752234</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>7729</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>2654940</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>461097674</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>7044</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>2748145</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>457432419</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>7396</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>2782476</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>448433709</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>7623</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>2751781</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>421254623</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>4465</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>3153810</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>432427422</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>4524</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>3095380</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>437779716</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>4669</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>3113206</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>443866587</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>4484</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>3227580</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>457312921</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>6366</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>2943751</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>460952021</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>6071</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>2716066</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>459510801</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>6456</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>2765465</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>459412429</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>6258</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>2792337</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>462645559</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>6537</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>2640265</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>467516265</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>6445</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>2389523</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>464254905</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>6849</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>2607243</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>463196399</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>6408</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>2480028</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>481422112</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>7406</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>2795678</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>475065653</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>7042</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>2544953</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>465721438</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>6922</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>2849914</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>472315318</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>7521</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>2907716</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>471720229</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>8008</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>3571962</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>473881480</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>7133</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>3399026</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>474498735</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>8192</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>3500765</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>483044075</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>8078</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>3676738</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>471094466</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>4078</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>3551486</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>464730846</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>5297</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>3444269</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>468089731</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>5496</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>3384432</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>474783710</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>5221</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>3613179</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>460467762</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>6462</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>3123471</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>464810197</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>6299</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>2995272</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>463566980</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>6993</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>3425721</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>467770165</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>6554</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>3218279</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>463609231</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>6963</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>3154984</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>465316148</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>6710</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>2655966</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>469588332</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>7229</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>2854753</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>466525534</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>7407</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>3147197</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>470280999</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>7529</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>3411659</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>483035998</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>7528</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>3426241</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>476417864</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>7797</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>3659848</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>472847179</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>7208</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>3441434</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>470096080</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>6976</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>3056723</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>475701535</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>7412</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>3329447</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>474730360</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>7473</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>3460084</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>481375348</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>7678</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>3717056</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>475390541</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>4340</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>3569514</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>455958591</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>5188</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>3625168</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>460761482</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>5604</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>3631294</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>465161353</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>4782</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>3665966</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>461407450</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>6718</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>3627928</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>465053165</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>6359</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>3291172</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>461218093</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>6971</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>3557966</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>472432385</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>6666</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>3761193</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>466800751</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>7074</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>3719865</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>471596407</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>6829</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>2970848</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>470153341</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>7470</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>3196667</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>477791948</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>7294</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>3561878</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>466498477</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>6861</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>3041431</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>480796409</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>7376</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>3134878</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>479203226</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>7719</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>3496733</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28">
         <v>474194186</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28">
         <v>7422</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28">
         <v>3207619</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>471831840</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>6960</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>3226620</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>480286703</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>7562</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>3624002</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>468809012</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>7211</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>3497731</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>479517721</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>7206</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29">
         <v>3532717</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>472218333</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>4804</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>3794825</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>460546480</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>5024</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>3801686</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>459702106</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>5655</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>3907572</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30">
         <v>462053649</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>5155</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30">
         <v>3957456</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>465964899</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>7045</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>4054504</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>468361264</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>6214</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>3175616</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>463203937</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>6562</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>3389405</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>469366826</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>6614</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31">
         <v>3645653</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>time(sec)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>10w.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>10w.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>10w.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>rr.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>rr.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>rr.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>thr.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>thr.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>thr.dTLB-load-misses</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>457996185</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>1670</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>2852243</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>435910709</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>1681</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>2491712</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>438193977</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>1503</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>2241043</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>437303511</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>1452</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>2566902</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>863404326</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2744</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>4557093</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>861204381</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>2848</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>4133349</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>858373161</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>2971</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>3834114</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>883576983</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>2747</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>4382695</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>775382868</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>2219</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>4009083</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>779835704</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>2383</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>3795791</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>781909202</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>2512</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>3547032</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>822628543</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>2303</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>4129309</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>419036665</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>2103</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>1799254</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>431409142</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>2426</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>1774302</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>425314914</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>2281</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>1741343</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>452884096</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>2645</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>1950098</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>516488205</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>2484</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>2929878</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>536871080</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>4381</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>3252955</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>553918670</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>4327</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>3181795</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>556566063</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>3096</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>3691265</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>647009713</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>3726</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>3600478</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>625843780</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>4585</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>3929455</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>571110716</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>3356</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>3325627</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>612357275</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>3761</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>3288718</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>599189351</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>3416</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>3011648</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>610157442</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>3395</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>2700629</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>680139494</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>4527</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>3211434</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>584493050</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>2731</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>2772469</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>593026283</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>3003</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>3175054</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>590238328</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>2816</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>2911721</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>518943889</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>2745</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>2561151</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>568024336</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>2700</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>2735543</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>558290540</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>2620</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>2677475</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>641108678</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>2454</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>3474516</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>554516163</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>3211</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>2601866</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>564717398</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>2642</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>2786953</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>583430400</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>2426</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>3103514</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>679241845</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>2566</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>3634527</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>594419037</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>2686</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>2970886</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>601481539</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>1919</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>3047876</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>637210771</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>2435</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>3370171</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>607977726</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>2614</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>3440175</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>638121144</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>2637</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>2904953</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>537863948</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>2261</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>3037376</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>613493500</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>2263</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>3311055</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>640635489</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>2124</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3561299</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>662279763</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>2256</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>3501622</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>571608801</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>1722</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>3117399</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>628693322</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>2189</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>3465056</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>575480549</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>1024</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>3147711</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>657319844</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>1359</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>3365011</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>579876634</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>2667</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>3320822</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>622420654</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>2745</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>3443181</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>713055782</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1199</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>3688129</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>656209834</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>1446</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>3025888</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>603966427</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>1792</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>3099356</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>662520636</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>2135</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>3719729</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>687135164</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>958</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>3717264</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>701593573</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>1517</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>3538704</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>636701929</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>1488</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>3569794</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>627848369</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>1918</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>3818848</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>633083460</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>1004</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>3197143</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>637591302</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>1362</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>3079150</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>498779492</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>1508</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>2429539</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>618893233</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>1046</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>2998325</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>649081755</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>1056</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>3857130</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>650664144</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>1131</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>3217462</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>512680360</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>1199</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>2662432</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>648705246</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>1268</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>3737046</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>665352072</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>990</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>3454374</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>669933877</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>1057</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>3295579</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>632498921</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>1270</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>3138785</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>675605308</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>1138</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>3737400</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>651571631</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>1059</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>3322145</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>646195513</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>1039</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>2890700</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>643880223</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>1351</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>3615556</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>647040381</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>1030</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>3868120</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>706219985</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>1115</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>4304797</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>658952008</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>1183</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>3438024</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>630080373</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>1358</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>3745901</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>679182008</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>1089</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>3877773</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>684967036</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>1152</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>3666870</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>624764533</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>955</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>3016252</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>531980243</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>1303</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>3229860</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>631111635</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>949</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>3626681</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>679039920</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>988</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>3663119</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>582655905</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>882</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>2828152</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>582643534</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>990</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>3095496</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>671262923</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>996</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>3876235</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>696008721</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>1083</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>4413764</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>682607779</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>1048</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>3454340</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>597287573</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>1132</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>3086020</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>691498980</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>1085</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>4292756</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>700202917</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>1247</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>4035630</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>716829477</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>1187</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>3775526</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>558127004</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>1046</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>3114962</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>637239441</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>897</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>3222964</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>676818624</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>1044</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>4194976</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>690043175</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>1154</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>3669289</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>618750426</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>886</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>3225874</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>640351521</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>1012</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>3899006</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>658937539</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>1139</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>3642414</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>624509709</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>1007</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>3243514</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>549869838</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>853</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>2919331</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>725123128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>1153</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>4357201</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>640189092</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>992</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>3487937</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>670380159</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>983</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>3086384</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28">
         <v>649483086</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28">
         <v>1061</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28">
         <v>3973091</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>659614550</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>1013</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>3663357</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>703032204</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>1141</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>4391311</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>643094814</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>936</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>3731651</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>635887788</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>895</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29">
         <v>3278772</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>645283403</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>917</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>3587338</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>693277263</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>1050</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>4337204</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>684222305</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>1041</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>3419634</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30">
         <v>635179151</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>1056</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30">
         <v>3378693</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>709278059</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>1064</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>4392485</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>706502247</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>1017</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>4116049</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>631351999</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>980</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>3283433</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>541030500</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>921</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31">
         <v>3394748</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>220494666</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>443</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>1312738</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>202884574</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>328</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>1164974</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>209100327</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>327</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32">
         <v>964610</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32">
         <v>131038019</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32">
         <v>265</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32">
         <v>676488</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>10853793</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>55</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>65969</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>10231520</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>47</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>69750</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>11035867</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>47</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33">
         <v>66492</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33">
         <v>10723813</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33">
         <v>49</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33">
         <v>69372</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>10972740</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>49</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>52543</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>16830527</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>73</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>151851</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34">
         <v>10180455</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>47</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34">
         <v>48789</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34">
         <v>8863547</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34">
         <v>50</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34">
         <v>51711</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>9281103</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>51</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>45846</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>11305703</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>52</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>67685</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>15217878</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>60</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35">
         <v>132649</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35">
         <v>10016739</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35">
         <v>45</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35">
         <v>44352</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>10070847</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>45</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>38188</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>8180811</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>46</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>34040</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>9748151</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>47</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36">
         <v>38569</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36">
         <v>9819050</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36">
         <v>44</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36">
         <v>37366</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>time(sec)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>10w.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>10w.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>10w.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>rr.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>rr.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>rr.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>thr.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>thr.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>thr.dTLB-load-misses</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>206623170</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>12253</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>821063</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>195220944</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>12471</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>930149</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>173381601</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>8261</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>723395</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>204375674</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>11515</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>885519</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>324506895</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>17169</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>907057</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>324026939</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>22743</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>1475298</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>250994414</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>12314</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>969934</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>324029548</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>19808</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>1415770</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>301663782</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>15257</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>898259</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>302111890</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>22019</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>1544776</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>235738126</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>12142</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>992547</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>304306930</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>17092</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>1343923</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>305478633</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>15685</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>1011521</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>305442970</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>22268</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>1658234</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>237099426</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>12686</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>1081197</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>306629311</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>16472</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>1396815</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>311800384</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>13261</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>1069620</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>312599446</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>22706</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>1804136</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>242080717</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>13094</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>1167341</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>306252810</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>13938</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>1419029</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>318518696</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>12571</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>1204321</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>317055666</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>21701</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>1898439</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>248026061</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>13217</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>1320391</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>321006713</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>12681</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>1652389</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>325687349</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>13662</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>1382776</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>317689173</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>18066</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>1937584</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>247870157</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>13709</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>1362171</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>324181143</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>13227</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>1747797</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>339179933</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>13880</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>1611904</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>324902073</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>12855</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1792117</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>254147278</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>14468</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>1488884</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>329803766</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>14303</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>1884405</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>351830024</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>13099</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>1874471</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>332120559</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>11951</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1888977</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>257437840</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>13291</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>1511391</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>342238059</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>15305</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>2141792</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>368552271</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>11155</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>2156359</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>345027932</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>10193</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2099335</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>262468554</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>12869</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>1649364</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>356414214</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>11572</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>2302848</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>393632937</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>3219</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>2393892</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>358698643</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>2804</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>2119841</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>268913504</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>13540</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>1790557</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>370239593</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>1570</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>2182063</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>424190620</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>219</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>2584719</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>394796986</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>798</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>2617629</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>278069119</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>14587</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>1995882</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>413577102</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>1068</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>2907125</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>515605394</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>198</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>3812202</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>451124926</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>1046</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>3443606</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>284886939</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>12816</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>2133650</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>481596963</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>190</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>3720873</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>724348799</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>356</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>6360821</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>576396810</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>414</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>5051523</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>292567567</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>3763</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>1980771</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>653827130</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>192</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>5916519</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>807205219</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>232</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>7640424</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>754269615</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>423</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>7314407</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>313135322</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>2366</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>2261239</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>776886250</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>210</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>7575168</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>741733831</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>178</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>7486437</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>794525177</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>170</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>7963516</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>348051371</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>722</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>2793680</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>766156807</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>166</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>7767571</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>818220651</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>170</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>8352907</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>783413289</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>318</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>8163789</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>404713514</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>555</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>3546155</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>800723737</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>237</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>8273187</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>866414742</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>166</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>8707901</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>830790702</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>171</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>8847748</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>538881555</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>174</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>5186556</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>859901591</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>274</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>8975604</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>879975039</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>161</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>8592072</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>852842658</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>162</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>8853557</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>771996651</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>266</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>7984386</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>849761254</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>159</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>8530227</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>887788487</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>207</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>8545232</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>877582642</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>191</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>8826704</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>748434023</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>241</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>7999844</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>872593313</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>175</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>8651287</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>882012319</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>224</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>8391949</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>906408817</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>225</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>8928774</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>777064494</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>158</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>8467894</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>835089881</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>210</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>8118697</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>865788709</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>227</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>8142697</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>892647270</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>224</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>8649961</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>834381701</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>163</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>9031487</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>872834197</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>238</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>8445963</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>855451071</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>187</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>7997307</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>890232007</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>225</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>8676606</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>882985482</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>190</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>9204893</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>904304086</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>252</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>8688505</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>868448179</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>185</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>8148161</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>871757421</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>219</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>8575510</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>906812235</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>204</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>9268453</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>885376690</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>298</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>8595340</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>892839150</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>188</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>8390881</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>872103561</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>239</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>8624845</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>880956080</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>192</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>8853814</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>857613657</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>231</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>8206762</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>893257907</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>200</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>8348522</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>872695006</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>218</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>8469664</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>905143744</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>198</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>8940491</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>883612309</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>220</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>8340730</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>902535702</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>202</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>8461350</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>901872069</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>213</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>8766596</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>882107905</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>201</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>8640840</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28">
         <v>871078823</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28">
         <v>192</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28">
         <v>8229247</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>890163396</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>223</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>8318873</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>890699821</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>198</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>8636540</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>870454755</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>218</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>8611574</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>873157170</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>174</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29">
         <v>8258197</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>894569876</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>222</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>8358876</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>888105417</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>206</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>8659780</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>876833329</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>232</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>8782282</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30">
         <v>880070490</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>230</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30">
         <v>8253407</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>882398634</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>184</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>8237081</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>869933774</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>229</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>8522350</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>898268908</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>236</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>9035100</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>888963189</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>236</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31">
         <v>8361883</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>time(sec)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>10w.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>10w.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>10w.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>cpu.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>rr.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>rr.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>rr.dTLB-load-misses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>thr.L1-dcache-load-misses</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>thr.cpu-migrations</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>thr.dTLB-load-misses</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>696444428</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>427</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>8319564</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>707030051</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>384</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>8757086</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>713701908</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>338</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>9714249</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>712880841</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>401</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>9626208</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1366676786</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>576</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>17886624</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>1375203995</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>469</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>18292629</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>1358058011</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>415</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>19362871</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>1369948891</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>454</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>19635458</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1396983488</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>1303</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>18952424</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>1429829799</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>1010</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>19679733</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>1365579307</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>965</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>20612329</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>1370833064</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>1088</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>20527594</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>692203376</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>4321</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>9592595</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>716114192</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>3229</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>10189303</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>689246432</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>5043</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>10631528</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>740892238</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>4442</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>11447805</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>780880453</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>2974</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>10825670</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>699527166</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>3206</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>9985106</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>777707739</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>3417</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>11894455</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>771401743</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>3020</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>11939301</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>740579675</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>2453</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>10183372</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>725338782</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>2836</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>10236484</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>719700705</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2158</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>10744364</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>702410682</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>2837</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>10830061</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>425906351</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>2815</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>5812746</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>420443977</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>3440</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>5924105</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>466495276</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>2084</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>6732706</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>613650922</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>2836</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>9706110</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>387770326</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2582</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>5205866</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>393989217</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>2288</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>5351073</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>412407665</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>1883</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>5881709</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>353251905</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>2973</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>6040674</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>518509023</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>1628</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>6840419</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>703545432</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>1131</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>9258500</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>535220629</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>1512</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>7544897</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>411545260</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>1914</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>6521376</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1384795126</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>326</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>18833383</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1407573889</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>278</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>19593119</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1393612323</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>276</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>20195308</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>1284343081</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>490</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>19877567</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>911441600</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>829</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>12042495</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>829365740</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>873</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>11120543</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>852692077</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>1057</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>12091329</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>1013664288</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>661</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>14936582</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>503331154</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>1323</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>6202374</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>497001825</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>1265</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>6107330</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>474666147</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>1472</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>6469574</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>678336923</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>1325</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>10025100</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>345258963</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>1366</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>3742453</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>365760640</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>1399</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>4061741</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>415029946</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>1433</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>5471308</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>390329103</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>1469</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>5554995</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>382878242</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>1393</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>4337484</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>400427141</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1345</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>4503250</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>397579928</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>1568</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>5225752</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>419513264</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>1635</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>6248164</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>735683727</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>979</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>9567995</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>632310119</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>1062</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>7907989</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>803746022</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>973</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>11195103</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>404873790</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>1525</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>5595806</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>1398788476</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>203</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>19090222</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>1399340179</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>271</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>19078753</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>1408728788</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>165</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>19913826</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>1387274082</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>322</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>19682127</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>875824941</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>861</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>11572241</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>972943438</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>692</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>12846922</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>809974460</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>855</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>10997431</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>1030000956</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>821</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>14452462</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>698284764</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>990</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>8979284</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>705605184</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>969</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>9109683</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>739834125</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>1128</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>9949704</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>755661122</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>1034</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>10340694</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>770650522</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>1043</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>9932272</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>793990647</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>937</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>10331356</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>754641742</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>1026</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>10147146</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>717185225</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>1158</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>9987013</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>722537808</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>964</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>9260369</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>730173317</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>1044</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>9399644</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>770207774</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>1020</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>10308398</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>789272982</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>959</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>10677644</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>757801177</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>1128</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>9830447</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>768461665</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>960</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>9884598</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>803939030</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>799</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>10761769</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>763423208</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>1047</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>10655290</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>632242432</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>1129</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>8061366</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>628820649</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>1030</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>7894325</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>563033302</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>1240</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>7632527</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>783227024</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>1009</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>10665219</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>388408133</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>1291</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>4421058</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>350194931</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>1391</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>3962004</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>406768592</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>1442</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>5308352</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>394369967</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>1443</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>5793281</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>1031781409</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>703</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>13382794</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>1017981149</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>741</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>12820913</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>975684279</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>729</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>13036125</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>608500085</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>1349</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>8275198</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>1004199247</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>694</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>12912490</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>953468768</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>839</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>12134469</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>933153333</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>789</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>12283896</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>1171545826</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>599</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>15602904</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>744269534</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>1113</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>9494508</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>763456828</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>1085</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>9607143</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>751203582</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>988</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>9966370</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>745806847</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>1264</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>10341624</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>585538541</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>1163</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>7225254</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>656051972</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>1149</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>8161875</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>650125680</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>1165</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>8348383</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28">
         <v>746055905</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28">
         <v>1232</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28">
         <v>10182195</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>327312116</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>1501</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>3676923</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>331439182</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>1633</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>3951505</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>376034502</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>1529</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>4661261</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>465692710</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>1432</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29">
         <v>5993042</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>359771268</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>1652</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>4204238</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>363144104</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>1632</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>4197036</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>325141526</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>1697</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>3892502</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30">
         <v>341752346</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>1692</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30">
         <v>4482909</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>599061430</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>1381</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>7372945</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>548731400</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>1535</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>6454595</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>505993100</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>1497</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>6370593</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>358599003</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>1657</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31">
         <v>4284631</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>481038427</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>201</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>4890977</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>491224218</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>123</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>4891858</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>540770042</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>158</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32">
         <v>5827410</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32">
         <v>207345349</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32">
         <v>600</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32">
         <v>1431522</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>164212003</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>81</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>505946</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>165351706</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>63</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>348392</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>160706624</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>66</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33">
         <v>385656</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33">
         <v>117449797</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33">
         <v>283</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33">
         <v>273018</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>